--- a/466-fix-juridiction/ig/ValueSet-tddui-patient-identifier.xlsx
+++ b/466-fix-juridiction/ig/ValueSet-tddui-patient-identifier.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T09:18:51+00:00</t>
+    <t>2026-05-07T09:25:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>
